--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.79398</v>
+        <v>17.49722</v>
       </c>
       <c r="D2" t="n">
-        <v>17.01939</v>
+        <v>16.777</v>
       </c>
       <c r="E2" t="n">
-        <v>17.50987</v>
+        <v>17.45983</v>
       </c>
       <c r="F2" t="n">
-        <v>43.89258</v>
+        <v>43.31193</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05337</v>
+        <v>0.05317</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84826</v>
+        <v>1.89409</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.40803</v>
+        <v>17.36904</v>
       </c>
       <c r="D3" t="n">
-        <v>16.90314</v>
+        <v>17.19181</v>
       </c>
       <c r="E3" t="n">
-        <v>17.01907</v>
+        <v>17.34987</v>
       </c>
       <c r="F3" t="n">
-        <v>44.56819</v>
+        <v>44.13426</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05182</v>
+        <v>0.05293</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88326</v>
+        <v>1.87225</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.25366</v>
+        <v>17.20306</v>
       </c>
       <c r="D4" t="n">
-        <v>17.01055</v>
+        <v>17.06942</v>
       </c>
       <c r="E4" t="n">
-        <v>17.61757</v>
+        <v>17.15966</v>
       </c>
       <c r="F4" t="n">
-        <v>43.51945</v>
+        <v>43.67694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05208</v>
+        <v>0.05178</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85097</v>
+        <v>1.89389</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.17883</v>
+        <v>17.19218</v>
       </c>
       <c r="D6" t="n">
-        <v>16.49133</v>
+        <v>16.23244</v>
       </c>
       <c r="E6" t="n">
-        <v>16.76383</v>
+        <v>17.19154</v>
       </c>
       <c r="F6" t="n">
-        <v>22.47789</v>
+        <v>22.26083</v>
       </c>
       <c r="G6" t="n">
-        <v>35.57563</v>
+        <v>35.19652</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.04372</v>
+        <v>16.93122</v>
       </c>
       <c r="D7" t="n">
-        <v>16.54947</v>
+        <v>16.35108</v>
       </c>
       <c r="E7" t="n">
-        <v>16.82866</v>
+        <v>16.80395</v>
       </c>
       <c r="F7" t="n">
-        <v>22.20944</v>
+        <v>22.71707</v>
       </c>
       <c r="G7" t="n">
-        <v>35.55326</v>
+        <v>34.64924</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.26775</v>
+        <v>17.06482</v>
       </c>
       <c r="D8" t="n">
-        <v>16.64278</v>
+        <v>16.46253</v>
       </c>
       <c r="E8" t="n">
-        <v>16.51894</v>
+        <v>16.78077</v>
       </c>
       <c r="F8" t="n">
-        <v>22.88411</v>
+        <v>22.27809</v>
       </c>
       <c r="G8" t="n">
-        <v>35.2704</v>
+        <v>35.06561</v>
       </c>
     </row>
   </sheetData>
